--- a/tests/webapp/fixtures/copilot_kuntolo.xlsx
+++ b/tests/webapp/fixtures/copilot_kuntolo.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="170">
   <si>
     <t xml:space="preserve">PUMPING TEST FIELD SHEET (STEP / CONSTANT DISCHARGE)</t>
   </si>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">Discharge note</t>
   </si>
   <si>
-    <t xml:space="preserve">Not measured (step 1: No bucket on site; the flow meter was not fitted.; step 2: No bucket on site; the flow meter was not fitted.; step 3: No bucket on site; the flow meter was not fitted.)</t>
+    <t xml:space="preserve">Not measured (step 1: No bucket on site; the flow meter was not fitted.; step 2: Bucket overflowed; a discharge of 1.2 m3/h by eye.; step 3: No bucket on site; the flow meter was not fitted.)</t>
   </si>
   <si>
     <t xml:space="preserve">Discharge per step (m3/h)</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">Step 1 discharge recorded as not measured: No bucket on site; the flow meter was not fitted.</t>
   </si>
   <si>
-    <t xml:space="preserve">Step 2 discharge recorded as not measured: No bucket on site; the flow meter was not fitted.</t>
+    <t xml:space="preserve">Step 2 discharge recorded as not measured: Bucket overflowed; a discharge of 1.2 m3/h by eye.</t>
   </si>
   <si>
     <t xml:space="preserve">Step 3 discharge recorded as not measured: No bucket on site; the flow meter was not fitted.</t>
@@ -516,6 +516,9 @@
   </si>
   <si>
     <t xml:space="preserve">No bucket on site; the flow meter was not fitted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bucket overflowed; a discharge of 1.2 m3/h by eye.</t>
   </si>
 </sst>
 </file>
@@ -3558,7 +3561,7 @@
         <v>167</v>
       </c>
       <c r="G105" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="106">
